--- a/Tasks/Task_704_ACTH_synthesis/reactions_additions.xlsx
+++ b/Tasks/Task_704_ACTH_synthesis/reactions_additions.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="26626"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="10102"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\Git\MSP_p3_2026_hormone_cytokine_task_creation\Current_files\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/emparsanjuliancano/Documents/GitHub/MSP_p3_2026_hormone_cytokine_task_creation/Tasks/Task_704_ACTH_synthesis/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7C90F20E-D9D8-4B72-91DE-F1DCA5358E7B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B18D4214-A6C1-E546-B250-21836DB53B68}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21240" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="500" windowWidth="28800" windowHeight="16180" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="rxns" sheetId="1" r:id="rId1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="14" uniqueCount="14">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="144" uniqueCount="95">
   <si>
     <t>action</t>
   </si>
@@ -78,13 +78,256 @@
   </si>
   <si>
     <t>project_notes_gene</t>
+  </si>
+  <si>
+    <t>MAR70400</t>
+  </si>
+  <si>
+    <t>synthesis of pre-proopiomelanocortin</t>
+  </si>
+  <si>
+    <t>signalling</t>
+  </si>
+  <si>
+    <t>pre-proopiomelanocortin-1 [c] --&gt; pre-proopiomelanocortin-2 [c]</t>
+  </si>
+  <si>
+    <t>ENSG00000115138</t>
+  </si>
+  <si>
+    <t>no</t>
+  </si>
+  <si>
+    <t>MAR70401</t>
+  </si>
+  <si>
+    <t>binding of SRP to pre-proopiomelanocortin</t>
+  </si>
+  <si>
+    <t>SRP process </t>
+  </si>
+  <si>
+    <t>pre-proopiomelanocortin-2[c] --&gt; pre-proopiomelanocortin-2-SRP [c]</t>
+  </si>
+  <si>
+    <t>ENSG00000143742 &amp; ENSG00000140319 &amp; ENSG00000153037 &amp; ENSG00000100883 &amp; ENSG00000167881 &amp; ENSG00000174780</t>
+  </si>
+  <si>
+    <t>pre-proopiomelanocortin</t>
+  </si>
+  <si>
+    <t>Task 704</t>
+  </si>
+  <si>
+    <t>SRP</t>
+  </si>
+  <si>
+    <t>MAR70402</t>
+  </si>
+  <si>
+    <t>transport to translocon of SRP-bound pre-pro-opiomelanocortin</t>
+  </si>
+  <si>
+    <t>SRP process</t>
+  </si>
+  <si>
+    <t>pre-pro-opiomelanocortin-2-SRP[r] + GTP → pre-pro-opiomelanocortin-2-SRP[t] + GDP</t>
+  </si>
+  <si>
+    <t>(ENSG00000182934 &amp; ENSG00000144867) &amp; ((ENSG00000058262 | ENSG00000065665) &amp; ENSG00000106803 &amp; ENSG00000132432)</t>
+  </si>
+  <si>
+    <t>SRP- receptor &amp; Sec61A1/2</t>
+  </si>
+  <si>
+    <t>MAR70403 </t>
+  </si>
+  <si>
+    <t>transport to ER of SRP-bound pre-pro-opiomelanocortin</t>
+  </si>
+  <si>
+    <t>pre-pro-opiomelanocortin-2-SRP[t] → pre-pro-opiomelanocortin-2-SRP[r]</t>
+  </si>
+  <si>
+    <t>MAR70404</t>
+  </si>
+  <si>
+    <t>cleavage of signal pepetide from pre-proopiomelanocortin</t>
+  </si>
+  <si>
+    <t>pre-pro-opiomelanocortin-2-SRP[r] -&gt; pro-opiomelanocortin-2-SRP[r] + signal-peptide[r]</t>
+  </si>
+  <si>
+    <t>(ENSG00000114902 &amp; ENSG00000129128 &amp; ENSG00000118363) &amp; (ENSG00000140612 | ENSG00000166562)</t>
+  </si>
+  <si>
+    <t>propiomolenocortin</t>
+  </si>
+  <si>
+    <t>SPC </t>
+  </si>
+  <si>
+    <t>MAR70405</t>
+  </si>
+  <si>
+    <t>ERO1-dependent production of hydrogen peroxide</t>
+  </si>
+  <si>
+    <t>protein folding</t>
+  </si>
+  <si>
+    <t>2 O2[r] + ERO1-4SH[r] -&gt; 2 H2O2 + ERO1-4S[r]</t>
+  </si>
+  <si>
+    <t>(ENSG00000197930 | ENSG00000086619)</t>
+  </si>
+  <si>
+    <t>ERO1</t>
+  </si>
+  <si>
+    <t>MAR70406</t>
+  </si>
+  <si>
+    <t>ERO1-catalyzed reoxidation of protein disulfide isomerase (PDI)</t>
+  </si>
+  <si>
+    <t>PDIA1-4SH[r] + ERO1-4S[r]-&gt; PDIA1-4S[r] + ERO1-4SH[r]</t>
+  </si>
+  <si>
+    <t>(ENSG00000197930 | ENSG00000086619) &amp; ENSG00000185624</t>
+  </si>
+  <si>
+    <t>ERO1 &amp; PDIA1</t>
+  </si>
+  <si>
+    <t>MAR70407</t>
+  </si>
+  <si>
+    <t>PDI-mediated addition of disulfide bonds to proopiomelanocortin</t>
+  </si>
+  <si>
+    <t>proopiomelanocortin-2-SRP[r] + PDIA1-4S[r] -&gt; proopiomelanocortin-2-SRP-oxidized-folded[r] + PDIA1 4SH[r]</t>
+  </si>
+  <si>
+    <t>ENSG00000185624</t>
+  </si>
+  <si>
+    <t>PDIA1</t>
+  </si>
+  <si>
+    <t>MAR70408</t>
+  </si>
+  <si>
+    <t>transport of proopiomelanocortin from ER to golgi</t>
+  </si>
+  <si>
+    <t>ER-golgi transport</t>
+  </si>
+  <si>
+    <t>proopiomelanocortin-2-SRP-oxidized-folded[er] -&gt; proopiomelanocortin-2-oxidized-folded[g]</t>
+  </si>
+  <si>
+    <t>(ENSG00000138802 | ENSG00000176986 | ENSG00000113615 | ENSG00000150961) &amp; ENSG00000148248 &amp; ENSG00000148396 &amp; ENSG00000138073 &amp; (ENSG00000152700 | ENSG00000079332) &amp; (ENSG00000138674 | ENSG00000075826) &amp; ENSG00000157020 &amp; (ENSG00000100934 | ENSG00000101310) </t>
+  </si>
+  <si>
+    <t>COPII &amp; COPI</t>
+  </si>
+  <si>
+    <t>MAR70409</t>
+  </si>
+  <si>
+    <t>formation of POMC aggregates</t>
+  </si>
+  <si>
+    <t>transport to granules </t>
+  </si>
+  <si>
+    <t>proopiomelanocortin-2-SRP-oxidized-folded [g] + granin → proopiomelanocortin-2-SRP-oxidized-folded aggregates [g] </t>
+  </si>
+  <si>
+    <t>MAR70410</t>
+  </si>
+  <si>
+    <t>formation of membrane bound POMC aggregates</t>
+  </si>
+  <si>
+    <t>proopiomelanocortin-2-SRP-oxidized-folded [g] aggregates → proopiomelanocortin-2-SRP-oxidized-folded membrane bound aggregates [g]</t>
+  </si>
+  <si>
+    <t>ENSG00000109472 &amp; ENSG00000104112 &amp; ENSG00000175115 &amp; ENSG00000117533</t>
+  </si>
+  <si>
+    <t>CPE &amp; SGIII &amp; PACS1</t>
+  </si>
+  <si>
+    <t>MAR70411</t>
+  </si>
+  <si>
+    <t>formation of immature granules containing POMC membrane bound aggregates</t>
+  </si>
+  <si>
+    <t>proopiomelanocortin-2-SRP-oxidized-folded membrane bound aggregates [g] → proopiomelanocortin-2-SRP-oxidized-folded [ig]</t>
+  </si>
+  <si>
+    <t>((ENSG00000072958 &amp; ENSG00000166747 &amp; ENSG00000100280 &amp; ENSG00000106367) I (ENSG00000185009 &amp; ENSG00000132842 &amp; ENSG00000177879)) &amp; (ENSG00000100083 &amp; ENSG00000103365)</t>
+  </si>
+  <si>
+    <t>AP1/3 &amp; GGA</t>
+  </si>
+  <si>
+    <t>MAR70412</t>
+  </si>
+  <si>
+    <t>maturation/acidification of immature granules containing POMC membrane bound aggregates</t>
+  </si>
+  <si>
+    <t>proopiomelanocortin-2-SRP-oxidized-folded membrane bound aggregates [ig]→ proopiomelanocortin-2-SRP-oxidized-folded membrane bound aggregates [mg]</t>
+  </si>
+  <si>
+    <t>ENSG00000104093 &amp; ENSG00000091157 &amp; ENSG00000163618 &amp; ENSG00000033627</t>
+  </si>
+  <si>
+    <t>DMXL2 AND WDR7 AND CAPS1 AND ATP6V0A1</t>
+  </si>
+  <si>
+    <t>MAR70413</t>
+  </si>
+  <si>
+    <t>cleavage of POMC/formation of pro-ACTH</t>
+  </si>
+  <si>
+    <t>proteolytic processing</t>
+  </si>
+  <si>
+    <t>proopiomelanocortin-2-SRP-oxidized-folded [mg] (PC1/3) → pro-ACTH</t>
+  </si>
+  <si>
+    <t>ENSG00000175426</t>
+  </si>
+  <si>
+    <t>pro-ACTH</t>
+  </si>
+  <si>
+    <t>PC1/3</t>
+  </si>
+  <si>
+    <t>MAR70414</t>
+  </si>
+  <si>
+    <t>cleavage of pro-ACTH/formation of ACTH</t>
+  </si>
+  <si>
+    <t>pro-ACTH (PC1/3) → ACTH</t>
+  </si>
+  <si>
+    <t>ACTH</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="2" x14ac:knownFonts="1">
+  <fonts count="7" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -97,6 +340,37 @@
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <color theme="1"/>
+      <name val="Arial"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF2A2A2A"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="12"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
     </font>
   </fonts>
   <fills count="2">
@@ -119,7 +393,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="9">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -128,6 +402,11 @@
       <alignment wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" quotePrefix="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -408,21 +687,21 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:N76"/>
-  <sheetFormatPr defaultColWidth="8.85546875" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <dimension ref="A1:P76"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="11.42578125" customWidth="1"/>
-    <col min="2" max="6" width="21.85546875" customWidth="1"/>
-    <col min="7" max="7" width="21.42578125" customWidth="1"/>
-    <col min="8" max="8" width="41.5703125" customWidth="1"/>
-    <col min="9" max="9" width="33.42578125" customWidth="1"/>
-    <col min="10" max="10" width="65.85546875" customWidth="1"/>
-    <col min="11" max="11" width="80.5703125" customWidth="1"/>
-    <col min="12" max="12" width="23.42578125" customWidth="1"/>
-    <col min="13" max="13" width="20.140625" customWidth="1"/>
+    <col min="1" max="1" width="11.5" customWidth="1"/>
+    <col min="2" max="6" width="21.83203125" customWidth="1"/>
+    <col min="7" max="7" width="21.5" customWidth="1"/>
+    <col min="8" max="8" width="41.5" customWidth="1"/>
+    <col min="9" max="9" width="33.5" customWidth="1"/>
+    <col min="10" max="10" width="65.83203125" customWidth="1"/>
+    <col min="11" max="11" width="80.5" customWidth="1"/>
+    <col min="12" max="12" width="23.5" customWidth="1"/>
+    <col min="13" max="13" width="20.1640625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -466,37 +745,444 @@
         <v>11</v>
       </c>
     </row>
-    <row r="3" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="L3" s="2"/>
-    </row>
-    <row r="4" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="L4" s="2"/>
-    </row>
-    <row r="5" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="L5" s="2"/>
-    </row>
-    <row r="7" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="L7" s="2"/>
-    </row>
-    <row r="8" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="L8" s="2"/>
-    </row>
-    <row r="10" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="L10" s="2"/>
-    </row>
-    <row r="12" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="L12" s="2"/>
-    </row>
-    <row r="14" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="L14" s="2"/>
-    </row>
-    <row r="16" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="L16" s="2"/>
-    </row>
-    <row r="18" spans="12:12" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="G2" t="s">
+        <v>14</v>
+      </c>
+      <c r="H2" t="s">
+        <v>15</v>
+      </c>
+      <c r="I2" t="s">
+        <v>16</v>
+      </c>
+      <c r="J2" t="s">
+        <v>17</v>
+      </c>
+      <c r="K2" t="s">
+        <v>18</v>
+      </c>
+      <c r="L2" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="3" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="G3" s="4" t="s">
+        <v>20</v>
+      </c>
+      <c r="H3" s="4" t="s">
+        <v>21</v>
+      </c>
+      <c r="I3" s="4" t="s">
+        <v>22</v>
+      </c>
+      <c r="J3" s="4" t="s">
+        <v>23</v>
+      </c>
+      <c r="K3" s="4" t="s">
+        <v>24</v>
+      </c>
+      <c r="L3" s="4" t="s">
+        <v>19</v>
+      </c>
+      <c r="M3" s="4" t="s">
+        <v>25</v>
+      </c>
+      <c r="N3" s="4" t="s">
+        <v>26</v>
+      </c>
+      <c r="O3" s="4" t="s">
+        <v>27</v>
+      </c>
+      <c r="P3" s="5"/>
+    </row>
+    <row r="4" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="G4" s="4" t="s">
+        <v>28</v>
+      </c>
+      <c r="H4" s="4" t="s">
+        <v>29</v>
+      </c>
+      <c r="I4" s="4" t="s">
+        <v>30</v>
+      </c>
+      <c r="J4" s="4" t="s">
+        <v>31</v>
+      </c>
+      <c r="K4" s="4" t="s">
+        <v>32</v>
+      </c>
+      <c r="L4" s="4" t="s">
+        <v>19</v>
+      </c>
+      <c r="M4" s="4" t="s">
+        <v>25</v>
+      </c>
+      <c r="N4" s="4" t="s">
+        <v>26</v>
+      </c>
+      <c r="O4" s="4" t="s">
+        <v>33</v>
+      </c>
+      <c r="P4" s="5"/>
+    </row>
+    <row r="5" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="G5" s="4" t="s">
+        <v>34</v>
+      </c>
+      <c r="H5" s="4" t="s">
+        <v>35</v>
+      </c>
+      <c r="I5" s="4" t="s">
+        <v>30</v>
+      </c>
+      <c r="J5" s="4" t="s">
+        <v>36</v>
+      </c>
+      <c r="K5" s="4" t="s">
+        <v>32</v>
+      </c>
+      <c r="L5" s="4" t="s">
+        <v>19</v>
+      </c>
+      <c r="M5" s="4" t="s">
+        <v>25</v>
+      </c>
+      <c r="N5" s="4" t="s">
+        <v>26</v>
+      </c>
+      <c r="O5" s="4" t="s">
+        <v>33</v>
+      </c>
+      <c r="P5" s="5"/>
+    </row>
+    <row r="6" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="G6" s="4" t="s">
+        <v>37</v>
+      </c>
+      <c r="H6" s="4" t="s">
+        <v>38</v>
+      </c>
+      <c r="I6" s="4" t="s">
+        <v>22</v>
+      </c>
+      <c r="J6" s="4" t="s">
+        <v>39</v>
+      </c>
+      <c r="K6" s="4" t="s">
+        <v>40</v>
+      </c>
+      <c r="L6" s="4" t="s">
+        <v>19</v>
+      </c>
+      <c r="M6" s="4" t="s">
+        <v>41</v>
+      </c>
+      <c r="N6" s="4" t="s">
+        <v>26</v>
+      </c>
+      <c r="O6" s="4" t="s">
+        <v>42</v>
+      </c>
+      <c r="P6" s="5"/>
+    </row>
+    <row r="7" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="G7" s="4" t="s">
+        <v>43</v>
+      </c>
+      <c r="H7" s="4" t="s">
+        <v>44</v>
+      </c>
+      <c r="I7" s="4" t="s">
+        <v>45</v>
+      </c>
+      <c r="J7" s="4" t="s">
+        <v>46</v>
+      </c>
+      <c r="K7" s="4" t="s">
+        <v>47</v>
+      </c>
+      <c r="L7" s="4" t="s">
+        <v>19</v>
+      </c>
+      <c r="M7" s="4" t="s">
+        <v>41</v>
+      </c>
+      <c r="N7" s="4" t="s">
+        <v>26</v>
+      </c>
+      <c r="O7" s="4" t="s">
+        <v>48</v>
+      </c>
+      <c r="P7" s="5"/>
+    </row>
+    <row r="8" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="G8" s="4" t="s">
+        <v>49</v>
+      </c>
+      <c r="H8" s="4" t="s">
+        <v>50</v>
+      </c>
+      <c r="I8" s="4" t="s">
+        <v>45</v>
+      </c>
+      <c r="J8" s="4" t="s">
+        <v>51</v>
+      </c>
+      <c r="K8" s="4" t="s">
+        <v>52</v>
+      </c>
+      <c r="L8" s="4" t="s">
+        <v>19</v>
+      </c>
+      <c r="M8" s="4" t="s">
+        <v>41</v>
+      </c>
+      <c r="N8" s="4" t="s">
+        <v>26</v>
+      </c>
+      <c r="O8" s="4" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="9" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="G9" s="4" t="s">
+        <v>54</v>
+      </c>
+      <c r="H9" s="4" t="s">
+        <v>55</v>
+      </c>
+      <c r="I9" s="4" t="s">
+        <v>45</v>
+      </c>
+      <c r="J9" s="4" t="s">
+        <v>56</v>
+      </c>
+      <c r="K9" s="4" t="s">
+        <v>57</v>
+      </c>
+      <c r="L9" s="4" t="s">
+        <v>19</v>
+      </c>
+      <c r="M9" s="4" t="s">
+        <v>41</v>
+      </c>
+      <c r="N9" s="4" t="s">
+        <v>26</v>
+      </c>
+      <c r="O9" s="4" t="s">
+        <v>58</v>
+      </c>
+      <c r="P9" s="5"/>
+    </row>
+    <row r="10" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="G10" s="4" t="s">
+        <v>59</v>
+      </c>
+      <c r="H10" s="4" t="s">
+        <v>60</v>
+      </c>
+      <c r="I10" s="4" t="s">
+        <v>61</v>
+      </c>
+      <c r="J10" s="6" t="s">
+        <v>62</v>
+      </c>
+      <c r="K10" s="4" t="s">
+        <v>63</v>
+      </c>
+      <c r="L10" s="4" t="s">
+        <v>19</v>
+      </c>
+      <c r="M10" s="4" t="s">
+        <v>41</v>
+      </c>
+      <c r="N10" s="4" t="s">
+        <v>26</v>
+      </c>
+      <c r="O10" s="4" t="s">
+        <v>64</v>
+      </c>
+      <c r="P10" s="5"/>
+    </row>
+    <row r="11" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="G11" s="4" t="s">
+        <v>65</v>
+      </c>
+      <c r="H11" s="4" t="s">
+        <v>66</v>
+      </c>
+      <c r="I11" s="4" t="s">
+        <v>67</v>
+      </c>
+      <c r="J11" s="4" t="s">
+        <v>68</v>
+      </c>
+      <c r="K11" s="5"/>
+      <c r="L11" s="4" t="s">
+        <v>19</v>
+      </c>
+      <c r="M11" s="4" t="s">
+        <v>41</v>
+      </c>
+      <c r="N11" s="4" t="s">
+        <v>26</v>
+      </c>
+      <c r="O11" s="5"/>
+      <c r="P11" s="5"/>
+    </row>
+    <row r="12" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="G12" s="4" t="s">
+        <v>69</v>
+      </c>
+      <c r="H12" s="4" t="s">
+        <v>70</v>
+      </c>
+      <c r="I12" s="4" t="s">
+        <v>67</v>
+      </c>
+      <c r="J12" s="7" t="s">
+        <v>71</v>
+      </c>
+      <c r="K12" s="4" t="s">
+        <v>72</v>
+      </c>
+      <c r="L12" s="4" t="s">
+        <v>19</v>
+      </c>
+      <c r="M12" s="4" t="s">
+        <v>41</v>
+      </c>
+      <c r="N12" s="4" t="s">
+        <v>26</v>
+      </c>
+      <c r="O12" s="4" t="s">
+        <v>73</v>
+      </c>
+      <c r="P12" s="5"/>
+    </row>
+    <row r="13" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="G13" s="4" t="s">
+        <v>74</v>
+      </c>
+      <c r="H13" s="4" t="s">
+        <v>75</v>
+      </c>
+      <c r="I13" s="4" t="s">
+        <v>67</v>
+      </c>
+      <c r="J13" s="7" t="s">
+        <v>76</v>
+      </c>
+      <c r="K13" s="4" t="s">
+        <v>77</v>
+      </c>
+      <c r="L13" s="4" t="s">
+        <v>19</v>
+      </c>
+      <c r="M13" s="4" t="s">
+        <v>41</v>
+      </c>
+      <c r="N13" s="4" t="s">
+        <v>26</v>
+      </c>
+      <c r="O13" s="4" t="s">
+        <v>78</v>
+      </c>
+      <c r="P13" s="5"/>
+    </row>
+    <row r="14" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="G14" s="4" t="s">
+        <v>79</v>
+      </c>
+      <c r="H14" s="4" t="s">
+        <v>80</v>
+      </c>
+      <c r="I14" s="4" t="s">
+        <v>67</v>
+      </c>
+      <c r="J14" s="7" t="s">
+        <v>81</v>
+      </c>
+      <c r="K14" s="4" t="s">
+        <v>82</v>
+      </c>
+      <c r="L14" s="4" t="s">
+        <v>19</v>
+      </c>
+      <c r="M14" s="4" t="s">
+        <v>41</v>
+      </c>
+      <c r="N14" s="4" t="s">
+        <v>26</v>
+      </c>
+      <c r="O14" s="4" t="s">
+        <v>83</v>
+      </c>
+      <c r="P14" s="5"/>
+    </row>
+    <row r="15" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="G15" s="4" t="s">
+        <v>84</v>
+      </c>
+      <c r="H15" s="4" t="s">
+        <v>85</v>
+      </c>
+      <c r="I15" s="4" t="s">
+        <v>86</v>
+      </c>
+      <c r="J15" s="4" t="s">
+        <v>87</v>
+      </c>
+      <c r="K15" s="4" t="s">
+        <v>88</v>
+      </c>
+      <c r="L15" s="4" t="s">
+        <v>19</v>
+      </c>
+      <c r="M15" s="4" t="s">
+        <v>89</v>
+      </c>
+      <c r="N15" s="4" t="s">
+        <v>26</v>
+      </c>
+      <c r="O15" s="4" t="s">
+        <v>90</v>
+      </c>
+      <c r="P15" s="5"/>
+    </row>
+    <row r="16" spans="1:16" ht="16" x14ac:dyDescent="0.2">
+      <c r="G16" s="4" t="s">
+        <v>91</v>
+      </c>
+      <c r="H16" s="4" t="s">
+        <v>92</v>
+      </c>
+      <c r="I16" s="4" t="s">
+        <v>86</v>
+      </c>
+      <c r="J16" s="4" t="s">
+        <v>93</v>
+      </c>
+      <c r="K16" s="4" t="s">
+        <v>88</v>
+      </c>
+      <c r="L16" s="4" t="s">
+        <v>19</v>
+      </c>
+      <c r="M16" s="4" t="s">
+        <v>94</v>
+      </c>
+      <c r="N16" s="4" t="s">
+        <v>26</v>
+      </c>
+      <c r="O16" s="8" t="s">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="18" spans="12:12" x14ac:dyDescent="0.2">
       <c r="L18" s="2"/>
     </row>
-    <row r="76" spans="12:12" x14ac:dyDescent="0.25">
+    <row r="76" spans="12:12" x14ac:dyDescent="0.2">
       <c r="L76" s="3"/>
     </row>
   </sheetData>
